--- a/old/260705.xlsx
+++ b/old/260705.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C393FAD-38D9-4AAF-91B0-152D56D61D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1392AEC7-FCF9-4FF5-A5DA-063694109C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4130" yWindow="3850" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -404,21 +403,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="26.58203125" customWidth="1"/>
-    <col min="3" max="3" width="24.5" customWidth="1"/>
-    <col min="4" max="4" width="24.25" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>